--- a/Exp3_PTO_GRPO/eda/results/arms/stats/tables/claude-haiku-4-5/stats.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/stats/tables/claude-haiku-4-5/stats.xlsx
@@ -980,13 +980,13 @@
         <v>1.834</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>0.963</v>
+        <v>1.069</v>
       </c>
       <c r="G11" t="n">
-        <v>1.422</v>
+        <v>1.702</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -997,16 +997,16 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.83</v>
+        <v>0.944</v>
       </c>
       <c r="K11" t="n">
-        <v>1.098</v>
+        <v>1.2</v>
       </c>
       <c r="L11" t="n">
-        <v>0.458</v>
+        <v>0.47</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2135</v>
+        <v>0.1911</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1032,13 +1032,13 @@
         <v>2.165</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>0.645</v>
+        <v>0.795</v>
       </c>
       <c r="G12" t="n">
-        <v>0.96</v>
+        <v>1.253</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1049,16 +1049,16 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.511</v>
+        <v>0.667</v>
       </c>
       <c r="K12" t="n">
-        <v>0.776</v>
+        <v>0.923</v>
       </c>
       <c r="L12" t="n">
-        <v>0.246</v>
+        <v>0.262</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1482</v>
+        <v>0.1358</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1084,13 +1084,13 @@
         <v>2.091</v>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>0.645</v>
+        <v>0.784</v>
       </c>
       <c r="G13" t="n">
-        <v>0.965</v>
+        <v>1.222</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1101,16 +1101,16 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.514</v>
+        <v>0.656</v>
       </c>
       <c r="K13" t="n">
-        <v>0.776</v>
+        <v>0.914</v>
       </c>
       <c r="L13" t="n">
-        <v>0.256</v>
+        <v>0.269</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1498</v>
+        <v>0.136</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1136,13 +1136,13 @@
         <v>2.439</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>0.658</v>
+        <v>0.793</v>
       </c>
       <c r="G14" t="n">
-        <v>0.974</v>
+        <v>1.114</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1153,16 +1153,16 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.524</v>
+        <v>0.656</v>
       </c>
       <c r="K14" t="n">
-        <v>0.793</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>0.247</v>
+        <v>0.263</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1488</v>
+        <v>0.135</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1188,33 +1188,33 @@
         <v>1.831</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>0.354</v>
+        <v>0.513</v>
       </c>
       <c r="G15" t="n">
-        <v>0.705</v>
+        <v>0.885</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.247</v>
+        <v>0.401</v>
       </c>
       <c r="K15" t="n">
-        <v>0.451</v>
+        <v>0.625</v>
       </c>
       <c r="L15" t="n">
-        <v>0.229</v>
+        <v>0.241</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0776</v>
+        <v>0.0736</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1240,13 +1240,13 @@
         <v>0.507</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>0.116</v>
+        <v>0.171</v>
       </c>
       <c r="G16" t="n">
-        <v>0.539</v>
+        <v>0.751</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1257,16 +1257,16 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.074</v>
+        <v>0.126</v>
       </c>
       <c r="K16" t="n">
-        <v>0.161</v>
+        <v>0.219</v>
       </c>
       <c r="L16" t="n">
-        <v>0.137</v>
+        <v>0.159</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0293</v>
+        <v>0.0287</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1292,33 +1292,33 @@
         <v>0.326</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>0.32</v>
+        <v>0.249</v>
       </c>
       <c r="G17" t="n">
-        <v>0.855</v>
+        <v>0.672</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.248</v>
+        <v>0.175</v>
       </c>
       <c r="K17" t="n">
-        <v>0.399</v>
+        <v>0.321</v>
       </c>
       <c r="L17" t="n">
-        <v>0.405</v>
+        <v>0.382</v>
       </c>
       <c r="M17" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0539</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1344,13 +1344,13 @@
         <v>1.681</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>1.129</v>
+        <v>1.217</v>
       </c>
       <c r="G18" t="n">
-        <v>1.348</v>
+        <v>1.613</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1361,16 +1361,16 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.96</v>
+        <v>1.062</v>
       </c>
       <c r="K18" t="n">
-        <v>1.292</v>
+        <v>1.369</v>
       </c>
       <c r="L18" t="n">
-        <v>0.45</v>
+        <v>0.459</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2576</v>
+        <v>0.2273</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1396,13 +1396,13 @@
         <v>1.988</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>0.797</v>
+        <v>0.921</v>
       </c>
       <c r="G19" t="n">
-        <v>1.247</v>
+        <v>1.433</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1413,16 +1413,16 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.67</v>
+        <v>0.793</v>
       </c>
       <c r="K19" t="n">
-        <v>0.931</v>
+        <v>1.055</v>
       </c>
       <c r="L19" t="n">
-        <v>0.417</v>
+        <v>0.439</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1693</v>
+        <v>0.1549</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2852,13 +2852,13 @@
         <v>1.834</v>
       </c>
       <c r="E47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F47" t="n">
-        <v>0.963</v>
+        <v>1.069</v>
       </c>
       <c r="G47" t="n">
-        <v>1.422</v>
+        <v>1.702</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2869,16 +2869,16 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0.83</v>
+        <v>0.944</v>
       </c>
       <c r="K47" t="n">
-        <v>1.098</v>
+        <v>1.2</v>
       </c>
       <c r="L47" t="n">
-        <v>0.458</v>
+        <v>0.47</v>
       </c>
       <c r="M47" t="n">
-        <v>0.2135</v>
+        <v>0.1911</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -2904,13 +2904,13 @@
         <v>2.165</v>
       </c>
       <c r="E48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F48" t="n">
-        <v>0.645</v>
+        <v>0.795</v>
       </c>
       <c r="G48" t="n">
-        <v>0.96</v>
+        <v>1.253</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2921,16 +2921,16 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.511</v>
+        <v>0.667</v>
       </c>
       <c r="K48" t="n">
-        <v>0.776</v>
+        <v>0.923</v>
       </c>
       <c r="L48" t="n">
-        <v>0.246</v>
+        <v>0.262</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1482</v>
+        <v>0.1358</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -2956,13 +2956,13 @@
         <v>2.091</v>
       </c>
       <c r="E49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
-        <v>0.645</v>
+        <v>0.784</v>
       </c>
       <c r="G49" t="n">
-        <v>0.965</v>
+        <v>1.222</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2973,16 +2973,16 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.514</v>
+        <v>0.656</v>
       </c>
       <c r="K49" t="n">
-        <v>0.776</v>
+        <v>0.914</v>
       </c>
       <c r="L49" t="n">
-        <v>0.256</v>
+        <v>0.269</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1498</v>
+        <v>0.136</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -3008,13 +3008,13 @@
         <v>2.439</v>
       </c>
       <c r="E50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F50" t="n">
-        <v>0.658</v>
+        <v>0.793</v>
       </c>
       <c r="G50" t="n">
-        <v>0.974</v>
+        <v>1.114</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3025,16 +3025,16 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0.524</v>
+        <v>0.656</v>
       </c>
       <c r="K50" t="n">
-        <v>0.793</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>0.247</v>
+        <v>0.263</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1488</v>
+        <v>0.135</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -3060,33 +3060,33 @@
         <v>1.831</v>
       </c>
       <c r="E51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F51" t="n">
-        <v>0.354</v>
+        <v>0.513</v>
       </c>
       <c r="G51" t="n">
-        <v>0.705</v>
+        <v>0.885</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0.247</v>
+        <v>0.401</v>
       </c>
       <c r="K51" t="n">
-        <v>0.451</v>
+        <v>0.625</v>
       </c>
       <c r="L51" t="n">
-        <v>0.229</v>
+        <v>0.241</v>
       </c>
       <c r="M51" t="n">
-        <v>0.0776</v>
+        <v>0.0736</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
@@ -3112,13 +3112,13 @@
         <v>0.507</v>
       </c>
       <c r="E52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F52" t="n">
-        <v>0.116</v>
+        <v>0.171</v>
       </c>
       <c r="G52" t="n">
-        <v>0.539</v>
+        <v>0.751</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3129,16 +3129,16 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0.074</v>
+        <v>0.126</v>
       </c>
       <c r="K52" t="n">
-        <v>0.161</v>
+        <v>0.219</v>
       </c>
       <c r="L52" t="n">
-        <v>0.137</v>
+        <v>0.159</v>
       </c>
       <c r="M52" t="n">
-        <v>0.0293</v>
+        <v>0.0287</v>
       </c>
       <c r="N52" t="n">
         <v>0</v>
@@ -3164,33 +3164,33 @@
         <v>0.326</v>
       </c>
       <c r="E53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F53" t="n">
-        <v>0.32</v>
+        <v>0.249</v>
       </c>
       <c r="G53" t="n">
-        <v>0.855</v>
+        <v>0.672</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0.248</v>
+        <v>0.175</v>
       </c>
       <c r="K53" t="n">
-        <v>0.399</v>
+        <v>0.321</v>
       </c>
       <c r="L53" t="n">
-        <v>0.405</v>
+        <v>0.382</v>
       </c>
       <c r="M53" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0539</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -3216,13 +3216,13 @@
         <v>1.681</v>
       </c>
       <c r="E54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F54" t="n">
-        <v>1.129</v>
+        <v>1.217</v>
       </c>
       <c r="G54" t="n">
-        <v>1.348</v>
+        <v>1.613</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3233,16 +3233,16 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0.96</v>
+        <v>1.062</v>
       </c>
       <c r="K54" t="n">
-        <v>1.292</v>
+        <v>1.369</v>
       </c>
       <c r="L54" t="n">
-        <v>0.45</v>
+        <v>0.459</v>
       </c>
       <c r="M54" t="n">
-        <v>0.2576</v>
+        <v>0.2273</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
@@ -3268,13 +3268,13 @@
         <v>1.988</v>
       </c>
       <c r="E55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F55" t="n">
-        <v>0.797</v>
+        <v>0.921</v>
       </c>
       <c r="G55" t="n">
-        <v>1.247</v>
+        <v>1.433</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -3285,16 +3285,16 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0.67</v>
+        <v>0.793</v>
       </c>
       <c r="K55" t="n">
-        <v>0.931</v>
+        <v>1.055</v>
       </c>
       <c r="L55" t="n">
-        <v>0.417</v>
+        <v>0.439</v>
       </c>
       <c r="M55" t="n">
-        <v>0.1693</v>
+        <v>0.1549</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
@@ -4542,16 +4542,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>203.856</v>
+        <v>268.7236</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4247</v>
+        <v>0.4665</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
         <v>96</v>
@@ -4569,16 +4569,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>133.387</v>
+        <v>178.5589</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2779</v>
+        <v>0.31</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
         <v>96</v>
@@ -4596,16 +4596,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>125.6691</v>
+        <v>163.9144</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2618</v>
+        <v>0.2846</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
         <v>96</v>
@@ -4623,16 +4623,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>155.0354</v>
+        <v>193.836</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.323</v>
+        <v>0.3365</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
         <v>96</v>
@@ -4650,16 +4650,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>68.0949</v>
+        <v>88.46550000000001</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1419</v>
+        <v>0.1536</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G15" t="n">
         <v>96</v>
@@ -4677,16 +4677,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>44.3165</v>
+        <v>69.1223</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" t="n">
         <v>96</v>
@@ -4704,16 +4704,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>97.9532</v>
+        <v>113.1981</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2041</v>
+        <v>0.1965</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G17" t="n">
         <v>96</v>
@@ -4731,16 +4731,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>215.3761</v>
+        <v>272.3502</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4487</v>
+        <v>0.4728</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G18" t="n">
         <v>96</v>
@@ -4758,16 +4758,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>156.6403</v>
+        <v>216.6487</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3263</v>
+        <v>0.3761</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
         <v>96</v>
@@ -5270,7 +5270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5788,32 +5788,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
         <v>96</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2419</v>
+        <v>1.0688</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3566</v>
+        <v>1.7024</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0008</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0008</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1056</v>
+        <v>0.9439</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3702</v>
+        <v>1.1995</v>
       </c>
     </row>
     <row r="18">
@@ -5823,28 +5823,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
         <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3695</v>
+        <v>0.2419</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5113</v>
+        <v>0.3566</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2308</v>
+        <v>0.1056</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5184</v>
+        <v>0.3702</v>
       </c>
     </row>
     <row r="19">
@@ -5854,16 +5854,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>96</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6505</v>
+        <v>0.3695</v>
       </c>
       <c r="E19" t="n">
-        <v>0.862</v>
+        <v>0.5113</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -5872,10 +5872,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4949</v>
+        <v>0.2308</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8027</v>
+        <v>0.5184</v>
       </c>
     </row>
     <row r="20">
@@ -5885,16 +5885,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
         <v>96</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8507</v>
+        <v>0.6505</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1645</v>
+        <v>0.862</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -5903,10 +5903,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7002</v>
+        <v>0.4949</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9961</v>
+        <v>0.8027</v>
       </c>
     </row>
     <row r="21">
@@ -5916,16 +5916,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
         <v>96</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9222</v>
+        <v>0.8507</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2866</v>
+        <v>1.1645</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -5934,10 +5934,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7795</v>
+        <v>0.7002</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0662</v>
+        <v>0.9961</v>
       </c>
     </row>
     <row r="22">
@@ -5947,16 +5947,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
         <v>96</v>
       </c>
       <c r="D22" t="n">
-        <v>1.0199</v>
+        <v>0.9222</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3975</v>
+        <v>1.2866</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -5965,10 +5965,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.7795</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1645</v>
+        <v>1.0662</v>
       </c>
     </row>
     <row r="23">
@@ -5978,16 +5978,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
         <v>96</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9835</v>
+        <v>1.0199</v>
       </c>
       <c r="E23" t="n">
-        <v>1.3277</v>
+        <v>1.3975</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -5996,10 +5996,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8337</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1293</v>
+        <v>1.1645</v>
       </c>
     </row>
     <row r="24">
@@ -6009,16 +6009,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24" t="n">
         <v>96</v>
       </c>
       <c r="D24" t="n">
-        <v>1.0657</v>
+        <v>0.9835</v>
       </c>
       <c r="E24" t="n">
-        <v>1.3621</v>
+        <v>1.3277</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -6027,10 +6027,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9143</v>
+        <v>0.8337</v>
       </c>
       <c r="I24" t="n">
-        <v>1.2213</v>
+        <v>1.1293</v>
       </c>
     </row>
     <row r="25">
@@ -6040,16 +6040,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C25" t="n">
         <v>96</v>
       </c>
       <c r="D25" t="n">
-        <v>1.0914</v>
+        <v>1.0657</v>
       </c>
       <c r="E25" t="n">
-        <v>1.6207</v>
+        <v>1.3621</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -6058,10 +6058,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9616</v>
+        <v>0.9143</v>
       </c>
       <c r="I25" t="n">
-        <v>1.2255</v>
+        <v>1.2213</v>
       </c>
     </row>
     <row r="26">
@@ -6071,16 +6071,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C26" t="n">
         <v>96</v>
       </c>
       <c r="D26" t="n">
-        <v>1.0363</v>
+        <v>1.0914</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6527</v>
+        <v>1.6207</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -6089,41 +6089,41 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9123</v>
+        <v>0.9616</v>
       </c>
       <c r="I26" t="n">
-        <v>1.1573</v>
+        <v>1.2255</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C27" t="n">
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1778</v>
+        <v>1.0363</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2307</v>
+        <v>1.6527</v>
       </c>
       <c r="F27" t="n">
-        <v>0.07920000000000001</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.07920000000000001</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0238</v>
+        <v>0.9123</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3331</v>
+        <v>1.1573</v>
       </c>
     </row>
     <row r="28">
@@ -6133,28 +6133,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2294</v>
+        <v>0.1778</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3189</v>
+        <v>0.2307</v>
       </c>
       <c r="F28" t="n">
-        <v>0.004</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.0238</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3715</v>
+        <v>0.3331</v>
       </c>
     </row>
     <row r="29">
@@ -6164,28 +6164,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
         <v>96</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5162</v>
+        <v>0.2294</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6611</v>
+        <v>0.3189</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3559</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6763</v>
+        <v>0.3715</v>
       </c>
     </row>
     <row r="30">
@@ -6195,16 +6195,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
         <v>96</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7237</v>
+        <v>0.5162</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9418</v>
+        <v>0.6611</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -6213,10 +6213,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5644</v>
+        <v>0.3559</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8784</v>
+        <v>0.6763</v>
       </c>
     </row>
     <row r="31">
@@ -6226,16 +6226,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7451</v>
+        <v>0.7237</v>
       </c>
       <c r="E31" t="n">
-        <v>1.0549</v>
+        <v>0.9418</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -6244,10 +6244,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6086</v>
+        <v>0.5644</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8832</v>
+        <v>0.8784</v>
       </c>
     </row>
     <row r="32">
@@ -6257,16 +6257,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>0.673</v>
+        <v>0.7451</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8837</v>
+        <v>1.0549</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -6275,10 +6275,10 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5214</v>
+        <v>0.6086</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8336</v>
+        <v>0.8832</v>
       </c>
     </row>
     <row r="33">
@@ -6288,16 +6288,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C33" t="n">
         <v>96</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9016</v>
+        <v>0.673</v>
       </c>
       <c r="E33" t="n">
-        <v>1.3064</v>
+        <v>0.8837</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -6306,10 +6306,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.5214</v>
       </c>
       <c r="I33" t="n">
-        <v>1.0451</v>
+        <v>0.8336</v>
       </c>
     </row>
     <row r="34">
@@ -6319,16 +6319,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C34" t="n">
         <v>96</v>
       </c>
       <c r="D34" t="n">
-        <v>0.876</v>
+        <v>0.9016</v>
       </c>
       <c r="E34" t="n">
-        <v>1.1013</v>
+        <v>1.3064</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -6337,10 +6337,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7145</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>1.0329</v>
+        <v>1.0451</v>
       </c>
     </row>
     <row r="35">
@@ -6350,16 +6350,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C35" t="n">
         <v>96</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8999</v>
+        <v>0.876</v>
       </c>
       <c r="E35" t="n">
-        <v>1.0834</v>
+        <v>1.1013</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -6368,10 +6368,10 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7297</v>
+        <v>0.7145</v>
       </c>
       <c r="I35" t="n">
-        <v>1.0589</v>
+        <v>1.0329</v>
       </c>
     </row>
     <row r="36">
@@ -6381,27 +6381,58 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C36" t="n">
         <v>96</v>
       </c>
       <c r="D36" t="n">
+        <v>0.8999</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.0834</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.7297</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.0589</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>10</v>
+      </c>
+      <c r="C37" t="n">
+        <v>96</v>
+      </c>
+      <c r="D37" t="n">
         <v>0.8333</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E37" t="n">
         <v>1.1241</v>
       </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
         <v>0.6907</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I37" t="n">
         <v>0.9809</v>
       </c>
     </row>
@@ -6679,16 +6710,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.4577</v>
+        <v>0.47</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2135</v>
+        <v>0.1911</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -6703,16 +6734,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.2462</v>
+        <v>0.2621</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1482</v>
+        <v>0.1358</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -6727,16 +6758,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2559</v>
+        <v>0.2693</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1498</v>
+        <v>0.136</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -6751,16 +6782,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2472</v>
+        <v>0.2626</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1488</v>
+        <v>0.135</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -6775,16 +6806,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.2293</v>
+        <v>0.2413</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0776</v>
+        <v>0.0736</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -6799,16 +6830,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.1374</v>
+        <v>0.159</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0293</v>
+        <v>0.0287</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -6823,16 +6854,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.4052</v>
+        <v>0.3816</v>
       </c>
       <c r="D17" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0539</v>
       </c>
       <c r="E17" t="n">
         <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -6847,16 +6878,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.4498</v>
+        <v>0.4594</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2576</v>
+        <v>0.2273</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -6871,16 +6902,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.417</v>
+        <v>0.4392</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1693</v>
+        <v>0.1549</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">

--- a/Exp3_PTO_GRPO/eda/results/arms/stats/tables/claude-haiku-4-5/stats.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/stats/tables/claude-haiku-4-5/stats.xlsx
@@ -980,13 +980,13 @@
         <v>1.834</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>1.069</v>
+        <v>1.038</v>
       </c>
       <c r="G11" t="n">
-        <v>1.702</v>
+        <v>1.539</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -997,16 +997,16 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.944</v>
+        <v>0.909</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2</v>
+        <v>1.177</v>
       </c>
       <c r="L11" t="n">
-        <v>0.47</v>
+        <v>0.383</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1911</v>
+        <v>0.101</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1032,13 +1032,13 @@
         <v>2.165</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>0.795</v>
+        <v>0.793</v>
       </c>
       <c r="G12" t="n">
-        <v>1.253</v>
+        <v>1.304</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1049,16 +1049,16 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.667</v>
+        <v>0.676</v>
       </c>
       <c r="K12" t="n">
-        <v>0.923</v>
+        <v>0.911</v>
       </c>
       <c r="L12" t="n">
-        <v>0.262</v>
+        <v>0.239</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1358</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1084,13 +1084,13 @@
         <v>2.091</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>0.784</v>
+        <v>0.844</v>
       </c>
       <c r="G13" t="n">
-        <v>1.222</v>
+        <v>1.43</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1101,16 +1101,16 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.656</v>
+        <v>0.73</v>
       </c>
       <c r="K13" t="n">
-        <v>0.914</v>
+        <v>0.964</v>
       </c>
       <c r="L13" t="n">
-        <v>0.269</v>
+        <v>0.246</v>
       </c>
       <c r="M13" t="n">
-        <v>0.136</v>
+        <v>0.0786</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1136,13 +1136,13 @@
         <v>2.439</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>0.793</v>
+        <v>0.889</v>
       </c>
       <c r="G14" t="n">
-        <v>1.114</v>
+        <v>1.234</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1153,16 +1153,16 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.656</v>
+        <v>0.753</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9389999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="L14" t="n">
         <v>0.263</v>
       </c>
       <c r="M14" t="n">
-        <v>0.135</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1188,13 +1188,13 @@
         <v>1.831</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>0.513</v>
+        <v>0.544</v>
       </c>
       <c r="G15" t="n">
-        <v>0.885</v>
+        <v>0.881</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1205,16 +1205,16 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.401</v>
+        <v>0.417</v>
       </c>
       <c r="K15" t="n">
-        <v>0.625</v>
+        <v>0.667</v>
       </c>
       <c r="L15" t="n">
-        <v>0.241</v>
+        <v>0.204</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0736</v>
+        <v>0.0493</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1240,33 +1240,33 @@
         <v>0.507</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F16" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
         <v>0.171</v>
       </c>
-      <c r="G16" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.126</v>
-      </c>
       <c r="K16" t="n">
-        <v>0.219</v>
+        <v>0.267</v>
       </c>
       <c r="L16" t="n">
-        <v>0.159</v>
+        <v>0.208</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0287</v>
+        <v>0.0233</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1292,33 +1292,33 @@
         <v>0.326</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>0.249</v>
+        <v>0.301</v>
       </c>
       <c r="G17" t="n">
-        <v>0.672</v>
+        <v>0.845</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.175</v>
+        <v>0.233</v>
       </c>
       <c r="K17" t="n">
-        <v>0.321</v>
+        <v>0.372</v>
       </c>
       <c r="L17" t="n">
-        <v>0.382</v>
+        <v>0.322</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0539</v>
+        <v>0.0276</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1344,13 +1344,13 @@
         <v>1.681</v>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>1.217</v>
+        <v>1.05</v>
       </c>
       <c r="G18" t="n">
-        <v>1.613</v>
+        <v>1.228</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1361,16 +1361,16 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.062</v>
+        <v>0.887</v>
       </c>
       <c r="K18" t="n">
-        <v>1.369</v>
+        <v>1.221</v>
       </c>
       <c r="L18" t="n">
-        <v>0.459</v>
+        <v>0.334</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2273</v>
+        <v>0.1051</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1396,13 +1396,13 @@
         <v>1.988</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>0.921</v>
+        <v>1.027</v>
       </c>
       <c r="G19" t="n">
-        <v>1.433</v>
+        <v>1.594</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1413,16 +1413,16 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.793</v>
+        <v>0.896</v>
       </c>
       <c r="K19" t="n">
-        <v>1.055</v>
+        <v>1.158</v>
       </c>
       <c r="L19" t="n">
-        <v>0.439</v>
+        <v>0.408</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1549</v>
+        <v>0.097</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2852,13 +2852,13 @@
         <v>1.834</v>
       </c>
       <c r="E47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F47" t="n">
-        <v>1.069</v>
+        <v>1.078</v>
       </c>
       <c r="G47" t="n">
-        <v>1.702</v>
+        <v>1.466</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2869,16 +2869,16 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0.944</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>1.2</v>
+        <v>1.228</v>
       </c>
       <c r="L47" t="n">
-        <v>0.47</v>
+        <v>0.383</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1911</v>
+        <v>0.101</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -2904,13 +2904,13 @@
         <v>2.165</v>
       </c>
       <c r="E48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F48" t="n">
-        <v>0.795</v>
+        <v>0.723</v>
       </c>
       <c r="G48" t="n">
-        <v>1.253</v>
+        <v>1.17</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2921,16 +2921,16 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.667</v>
+        <v>0.603</v>
       </c>
       <c r="K48" t="n">
-        <v>0.923</v>
+        <v>0.852</v>
       </c>
       <c r="L48" t="n">
-        <v>0.262</v>
+        <v>0.239</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1358</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -2956,13 +2956,13 @@
         <v>2.091</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F49" t="n">
-        <v>0.784</v>
+        <v>0.701</v>
       </c>
       <c r="G49" t="n">
-        <v>1.222</v>
+        <v>1.004</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2973,16 +2973,16 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.656</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>0.914</v>
+        <v>0.839</v>
       </c>
       <c r="L49" t="n">
-        <v>0.269</v>
+        <v>0.246</v>
       </c>
       <c r="M49" t="n">
-        <v>0.136</v>
+        <v>0.0786</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -3008,13 +3008,13 @@
         <v>2.439</v>
       </c>
       <c r="E50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F50" t="n">
-        <v>0.793</v>
+        <v>0.766</v>
       </c>
       <c r="G50" t="n">
-        <v>1.114</v>
+        <v>1.041</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3025,16 +3025,16 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0.656</v>
+        <v>0.623</v>
       </c>
       <c r="K50" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.917</v>
       </c>
       <c r="L50" t="n">
         <v>0.263</v>
       </c>
       <c r="M50" t="n">
-        <v>0.135</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -3060,13 +3060,13 @@
         <v>1.831</v>
       </c>
       <c r="E51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F51" t="n">
-        <v>0.513</v>
+        <v>0.552</v>
       </c>
       <c r="G51" t="n">
-        <v>0.885</v>
+        <v>1.013</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3077,16 +3077,16 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0.401</v>
+        <v>0.443</v>
       </c>
       <c r="K51" t="n">
-        <v>0.625</v>
+        <v>0.659</v>
       </c>
       <c r="L51" t="n">
-        <v>0.241</v>
+        <v>0.204</v>
       </c>
       <c r="M51" t="n">
-        <v>0.0736</v>
+        <v>0.0493</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
@@ -3112,13 +3112,13 @@
         <v>0.507</v>
       </c>
       <c r="E52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F52" t="n">
-        <v>0.171</v>
+        <v>0.161</v>
       </c>
       <c r="G52" t="n">
-        <v>0.751</v>
+        <v>0.736</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3129,16 +3129,16 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0.126</v>
+        <v>0.12</v>
       </c>
       <c r="K52" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="L52" t="n">
-        <v>0.159</v>
+        <v>0.208</v>
       </c>
       <c r="M52" t="n">
-        <v>0.0287</v>
+        <v>0.0233</v>
       </c>
       <c r="N52" t="n">
         <v>0</v>
@@ -3164,13 +3164,13 @@
         <v>0.326</v>
       </c>
       <c r="E53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F53" t="n">
-        <v>0.249</v>
+        <v>0.253</v>
       </c>
       <c r="G53" t="n">
-        <v>0.672</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3181,16 +3181,16 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0.175</v>
+        <v>0.183</v>
       </c>
       <c r="K53" t="n">
-        <v>0.321</v>
+        <v>0.329</v>
       </c>
       <c r="L53" t="n">
-        <v>0.382</v>
+        <v>0.322</v>
       </c>
       <c r="M53" t="n">
-        <v>0.0539</v>
+        <v>0.0276</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -3216,13 +3216,13 @@
         <v>1.681</v>
       </c>
       <c r="E54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F54" t="n">
-        <v>1.217</v>
+        <v>1.188</v>
       </c>
       <c r="G54" t="n">
-        <v>1.613</v>
+        <v>1.403</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3233,16 +3233,16 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>1.062</v>
+        <v>1.025</v>
       </c>
       <c r="K54" t="n">
-        <v>1.369</v>
+        <v>1.362</v>
       </c>
       <c r="L54" t="n">
-        <v>0.459</v>
+        <v>0.334</v>
       </c>
       <c r="M54" t="n">
-        <v>0.2273</v>
+        <v>0.1051</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
@@ -3268,13 +3268,13 @@
         <v>1.988</v>
       </c>
       <c r="E55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F55" t="n">
-        <v>0.921</v>
+        <v>0.968</v>
       </c>
       <c r="G55" t="n">
-        <v>1.433</v>
+        <v>1.338</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -3285,16 +3285,16 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0.793</v>
+        <v>0.822</v>
       </c>
       <c r="K55" t="n">
-        <v>1.055</v>
+        <v>1.112</v>
       </c>
       <c r="L55" t="n">
-        <v>0.439</v>
+        <v>0.408</v>
       </c>
       <c r="M55" t="n">
-        <v>0.1549</v>
+        <v>0.097</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
@@ -4542,16 +4542,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>268.7236</v>
+        <v>368.6102</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4665</v>
+        <v>0.384</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
         <v>96</v>
@@ -4569,16 +4569,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>178.5589</v>
+        <v>277.0336</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.31</v>
+        <v>0.2886</v>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
         <v>96</v>
@@ -4596,16 +4596,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>163.9144</v>
+        <v>282.3218</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2846</v>
+        <v>0.2941</v>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
         <v>96</v>
@@ -4623,16 +4623,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>193.836</v>
+        <v>304.035</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3365</v>
+        <v>0.3167</v>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G14" t="n">
         <v>96</v>
@@ -4650,16 +4650,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>88.46550000000001</v>
+        <v>135.0381</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1536</v>
+        <v>0.1407</v>
       </c>
       <c r="F15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G15" t="n">
         <v>96</v>
@@ -4677,16 +4677,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>69.1223</v>
+        <v>202.1029</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.12</v>
+        <v>0.2105</v>
       </c>
       <c r="F16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G16" t="n">
         <v>96</v>
@@ -4704,16 +4704,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>113.1981</v>
+        <v>151.4486</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1965</v>
+        <v>0.1578</v>
       </c>
       <c r="F17" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G17" t="n">
         <v>96</v>
@@ -4731,16 +4731,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>272.3502</v>
+        <v>335.3761</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4728</v>
+        <v>0.3494</v>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G18" t="n">
         <v>96</v>
@@ -4758,16 +4758,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>216.6487</v>
+        <v>351.3549</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3761</v>
+        <v>0.366</v>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G19" t="n">
         <v>96</v>
@@ -5270,7 +5270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5819,51 +5819,51 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
         <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2419</v>
+        <v>1.0775</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3566</v>
+        <v>1.4665</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0008</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0008</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1056</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3702</v>
+        <v>1.2279</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
         <v>96</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3695</v>
+        <v>0.9412</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5113</v>
+        <v>1.2595</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -5872,29 +5872,29 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2308</v>
+        <v>0.7975</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5184</v>
+        <v>1.0862</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
         <v>96</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6505</v>
+        <v>1.0238</v>
       </c>
       <c r="E20" t="n">
-        <v>0.862</v>
+        <v>1.3349</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -5903,29 +5903,29 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4949</v>
+        <v>0.8743</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8027</v>
+        <v>1.1752</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C21" t="n">
         <v>96</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8507</v>
+        <v>1.0385</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1645</v>
+        <v>1.5394</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -5934,10 +5934,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7002</v>
+        <v>0.9093</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9961</v>
+        <v>1.177</v>
       </c>
     </row>
     <row r="22">
@@ -5947,28 +5947,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
         <v>96</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9222</v>
+        <v>0.2419</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2866</v>
+        <v>0.3566</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7795</v>
+        <v>0.1056</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0662</v>
+        <v>0.3702</v>
       </c>
     </row>
     <row r="23">
@@ -5978,16 +5978,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
         <v>96</v>
       </c>
       <c r="D23" t="n">
-        <v>1.0199</v>
+        <v>0.3695</v>
       </c>
       <c r="E23" t="n">
-        <v>1.3975</v>
+        <v>0.5113</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -5996,10 +5996,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.2308</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1645</v>
+        <v>0.5184</v>
       </c>
     </row>
     <row r="24">
@@ -6009,16 +6009,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
         <v>96</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9835</v>
+        <v>0.6505</v>
       </c>
       <c r="E24" t="n">
-        <v>1.3277</v>
+        <v>0.862</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -6027,10 +6027,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8337</v>
+        <v>0.4949</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1293</v>
+        <v>0.8027</v>
       </c>
     </row>
     <row r="25">
@@ -6040,16 +6040,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
         <v>96</v>
       </c>
       <c r="D25" t="n">
-        <v>1.0657</v>
+        <v>0.8507</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3621</v>
+        <v>1.1645</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -6058,10 +6058,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9143</v>
+        <v>0.7002</v>
       </c>
       <c r="I25" t="n">
-        <v>1.2213</v>
+        <v>0.9961</v>
       </c>
     </row>
     <row r="26">
@@ -6071,16 +6071,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
         <v>96</v>
       </c>
       <c r="D26" t="n">
-        <v>1.0914</v>
+        <v>0.9222</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6207</v>
+        <v>1.2866</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -6089,10 +6089,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9616</v>
+        <v>0.7795</v>
       </c>
       <c r="I26" t="n">
-        <v>1.2255</v>
+        <v>1.0662</v>
       </c>
     </row>
     <row r="27">
@@ -6102,16 +6102,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>1.0363</v>
+        <v>1.0199</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6527</v>
+        <v>1.3975</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -6120,91 +6120,91 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9123</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1573</v>
+        <v>1.1645</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C28" t="n">
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1778</v>
+        <v>0.9835</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2307</v>
+        <v>1.3277</v>
       </c>
       <c r="F28" t="n">
-        <v>0.07920000000000001</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.07920000000000001</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0238</v>
+        <v>0.8337</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3331</v>
+        <v>1.1293</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C29" t="n">
         <v>96</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2294</v>
+        <v>1.0657</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3189</v>
+        <v>1.3621</v>
       </c>
       <c r="F29" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.007900000000000001</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.9143</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3715</v>
+        <v>1.2213</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C30" t="n">
         <v>96</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5162</v>
+        <v>1.0914</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6611</v>
+        <v>1.6207</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -6213,29 +6213,29 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3559</v>
+        <v>0.9616</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6763</v>
+        <v>1.2255</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C31" t="n">
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7237</v>
+        <v>1.0363</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9418</v>
+        <v>1.6527</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -6244,10 +6244,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5644</v>
+        <v>0.9123</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8784</v>
+        <v>1.1573</v>
       </c>
     </row>
     <row r="32">
@@ -6257,28 +6257,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7451</v>
+        <v>0.1778</v>
       </c>
       <c r="E32" t="n">
-        <v>1.0549</v>
+        <v>0.2307</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6086</v>
+        <v>0.0238</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8832</v>
+        <v>0.3331</v>
       </c>
     </row>
     <row r="33">
@@ -6288,28 +6288,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
         <v>96</v>
       </c>
       <c r="D33" t="n">
-        <v>0.673</v>
+        <v>0.2294</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8837</v>
+        <v>0.3189</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5214</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8336</v>
+        <v>0.3715</v>
       </c>
     </row>
     <row r="34">
@@ -6319,16 +6319,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C34" t="n">
         <v>96</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9016</v>
+        <v>0.5162</v>
       </c>
       <c r="E34" t="n">
-        <v>1.3064</v>
+        <v>0.6611</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -6337,10 +6337,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.3559</v>
       </c>
       <c r="I34" t="n">
-        <v>1.0451</v>
+        <v>0.6763</v>
       </c>
     </row>
     <row r="35">
@@ -6350,16 +6350,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C35" t="n">
         <v>96</v>
       </c>
       <c r="D35" t="n">
-        <v>0.876</v>
+        <v>0.7237</v>
       </c>
       <c r="E35" t="n">
-        <v>1.1013</v>
+        <v>0.9418</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -6368,10 +6368,10 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7145</v>
+        <v>0.5644</v>
       </c>
       <c r="I35" t="n">
-        <v>1.0329</v>
+        <v>0.8784</v>
       </c>
     </row>
     <row r="36">
@@ -6381,16 +6381,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C36" t="n">
         <v>96</v>
       </c>
       <c r="D36" t="n">
-        <v>0.8999</v>
+        <v>0.7451</v>
       </c>
       <c r="E36" t="n">
-        <v>1.0834</v>
+        <v>1.0549</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -6399,10 +6399,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7297</v>
+        <v>0.6086</v>
       </c>
       <c r="I36" t="n">
-        <v>1.0589</v>
+        <v>0.8832</v>
       </c>
     </row>
     <row r="37">
@@ -6412,27 +6412,151 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C37" t="n">
         <v>96</v>
       </c>
       <c r="D37" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8837</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.5214</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.8336</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>7</v>
+      </c>
+      <c r="C38" t="n">
+        <v>96</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.9016</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.3064</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.7606000000000001</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.0451</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>8</v>
+      </c>
+      <c r="C39" t="n">
+        <v>96</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.1013</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.7145</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.0329</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>9</v>
+      </c>
+      <c r="C40" t="n">
+        <v>96</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.8999</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.0834</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.7297</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.0589</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>10</v>
+      </c>
+      <c r="C41" t="n">
+        <v>96</v>
+      </c>
+      <c r="D41" t="n">
         <v>0.8333</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E41" t="n">
         <v>1.1241</v>
       </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
         <v>0.6907</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I41" t="n">
         <v>0.9809</v>
       </c>
     </row>
@@ -6710,16 +6834,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.47</v>
+        <v>0.3833</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1911</v>
+        <v>0.101</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -6734,16 +6858,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.2621</v>
+        <v>0.2386</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1358</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -6758,16 +6882,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2693</v>
+        <v>0.2459</v>
       </c>
       <c r="D13" t="n">
-        <v>0.136</v>
+        <v>0.0786</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -6782,16 +6906,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2626</v>
+        <v>0.263</v>
       </c>
       <c r="D14" t="n">
-        <v>0.135</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -6806,16 +6930,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.2413</v>
+        <v>0.2043</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0736</v>
+        <v>0.0493</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -6830,16 +6954,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.159</v>
+        <v>0.2084</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0287</v>
+        <v>0.0233</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -6854,16 +6978,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.3816</v>
+        <v>0.3216</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0539</v>
+        <v>0.0276</v>
       </c>
       <c r="E17" t="n">
         <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -6878,16 +7002,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.4594</v>
+        <v>0.3339</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2273</v>
+        <v>0.1051</v>
       </c>
       <c r="E18" t="n">
         <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -6902,16 +7026,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.4392</v>
+        <v>0.4083</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1549</v>
+        <v>0.097</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -7389,7 +7513,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54.5</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="4">
